--- a/丟/隨/2026 CITO OKR DRAFT.xlsx
+++ b/丟/隨/2026 CITO OKR DRAFT.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29910"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10222"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://pruo365.sharepoint.com/sites/EITWIT/Shared Documents/General/2026_OKR/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kaichanghuang/Documents/Phoenix Code/配息相關文件/DmsSystem/丟/隨/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DD54B2B6-6E61-4A6B-9169-C78F98B32615}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9BD2262-4574-7D4E-BAFB-F16429D60F95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="51200" windowHeight="27060" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="OKR_CITO" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="672" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="680" uniqueCount="146">
   <si>
     <t>Category</t>
   </si>
@@ -673,12 +673,88 @@
 	•	Document clear business benefits for each automation: quantify time saved (hours per month), error reduction (%), or improved SLA performance.</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
+  <si>
+    <t>Kent specific objectives to support</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Collaborated with the Eastspring Hong Kong team to design and deploy internal solutions using Power Automate, Power Apps, and SharePoint. These tools have successfully streamlined cross-regional workflows and enhanced operational efficiency, aligning with the 'One Eastspring' operating model.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Maintain the stability and performance of the core PowerBuilder system to support critical business functions. Focus on ensuring ≥ 99.5% uptime and resolving Tier-1 business application anomalies swiftly to prevent business impact.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Drive ownership and transparency in PB core system maintenance by strictly utilizing Jira and Remedyforce for demand management and prioritization. Ensure 100% of system change requests follow a clear RACI framework with documented business rationale and expected outcomes before execution.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Embrace a 'Client-First' culture by delivering exceptional and timely support for PB core systems through Jira and Remedyforce. Focus on clear communication and proactive problem-solving to consistently achieve an average CSAT score of &gt;= 4.5/5 from internal business users.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Reduce key person dependency for legacy infrastructure by developing comprehensive knowledge transfer (KT) materials for the all core PB systems. Cross-train at least 2 IT team members on critical troubleshooting and BAU processes to ensure uninterrupted business support.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Optimize the deployment process for PB core systems to compensate for the absence of a full CI/CD pipeline. Streamline manual Git version control and release procedures to reduce the average deployment time for new business features by 20%4</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Strictly enforce IT governance, access management, and change controls across all PB core systems (Investment, Customer, Operation, etc.) to protect sensitive business data. Proactively address and close 100% of IT audit findings on time, aiming for zero material audit issues in the 2026 annual audit.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Act as the primary technical and operational liaison for EC system vendors (Big Fun and Systemweb) to drive business outcomes. Ensure seamless project execution by managing resource/cost estimations, finalizing system requirements, and developing critical Stored Procedures for secure and efficient database integration.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Exercise strict financial discipline by meticulously evaluating resource quotes and consumption for EC system vendors (Big Fun, Systemweb).</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Demonstrate strict cost-saving discipline by optimizing the operating footprint of EC platforms. Rigorously review and renegotiate vendor resource quotes (Big Fun, Systemweb) to eliminate redundancies, aiming for a 10% reduction in specific external operational costs.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Act as a flexible capability resource within the region by providing continuous technical support and automation solutions (e.g., Power Platform) to the Hong Kong branch. Champion cross-border resource sharing to support the broader alternative resourcing objective.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Actively embody 'PruWays' values in daily IT operations by fostering open communication and seamless collaboration with both business units and IT peers. Fully support team engagement initiatives to help achieve the target PruVoice survey score of 60%+</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Drive positive changes in team engagement by addressing the primary negative theme from the 2025 People Survey. Streamline vendor management and demand intake processes (via Jira/Remedyforce) to create a more structured and less stressful working environment, contributing to a higher 2026 eNPS.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Actively contribute to the quarterly 'Digital Townhall' by presenting verifiable IT achievements and metrics. Highlight the impact of cross-functional initiatives, such as the deployment of automated workflows and PB core system enhancements, to drive business transparency and stakeholder alignment.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Finalize a personal skills development plan by Q3, approved by management, focusing on enhancing capabilities in vendor management and automated workflows. Support the team's 90% retention goal by proactively participating in cross-training and knowledge-sharing initiatives.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Drive the successful Q1 go-live of the 'New Master Agent' (Capital Group) strategic initiative on the legacy PB core systems. Ensure seamless system integration and robust data processing, while tightly controlling residual operational risks during the rollout to support broader business growth.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Support the successful delivery of the Taiwan TA initiative (Project Phoenix) by systematically extracting and documenting critical business rules from legacy PB source code. Provide precise business logic mapping to ensure the new data platform is built with high accuracy and aligns with Regional data governance standards by Q3.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Collaborate with the AP team to implement a foundational CI/CD pipeline by leveraging existing Git version control. Automate manual code deployment processes to improve delivery speed, targeting a 20% reduction in deployment time and ensuring full traceability between Jira tickets and source code changes.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -1011,18 +1087,18 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:G21"/>
-  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.5" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="27.85546875" style="2" customWidth="1"/>
-    <col min="2" max="2" width="41.5703125" style="2" customWidth="1"/>
-    <col min="3" max="3" width="20.42578125" style="2" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="27.83203125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="41.5" style="2" customWidth="1"/>
+    <col min="3" max="3" width="20.5" style="2" hidden="1" customWidth="1"/>
     <col min="4" max="5" width="0" style="2" hidden="1" customWidth="1"/>
     <col min="6" max="6" width="59" style="2" customWidth="1"/>
-    <col min="7" max="7" width="102.42578125" style="2" customWidth="1"/>
-    <col min="8" max="16384" width="12.5703125" style="2"/>
+    <col min="7" max="7" width="102.5" style="2" customWidth="1"/>
+    <col min="8" max="16384" width="12.5" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="5" customFormat="1" ht="18">
+    <row r="1" spans="1:7" s="5" customFormat="1" ht="38" x14ac:dyDescent="0.15">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1045,7 +1121,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="72">
+    <row r="2" spans="1:7" ht="57" x14ac:dyDescent="0.15">
       <c r="A2" s="8" t="s">
         <v>7</v>
       </c>
@@ -1068,7 +1144,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="180">
+    <row r="3" spans="1:7" ht="190" x14ac:dyDescent="0.15">
       <c r="A3" s="8"/>
       <c r="B3" s="1" t="s">
         <v>13</v>
@@ -1089,7 +1165,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="126">
+    <row r="4" spans="1:7" ht="133" x14ac:dyDescent="0.15">
       <c r="A4" s="8"/>
       <c r="B4" s="1" t="s">
         <v>17</v>
@@ -1104,7 +1180,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="179.1" customHeight="1">
+    <row r="5" spans="1:7" ht="179" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="8"/>
       <c r="B5" s="1" t="s">
         <v>20</v>
@@ -1119,7 +1195,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="108">
+    <row r="6" spans="1:7" ht="95" x14ac:dyDescent="0.15">
       <c r="A6" s="8"/>
       <c r="B6" s="1" t="s">
         <v>23</v>
@@ -1140,7 +1216,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="72">
+    <row r="7" spans="1:7" ht="76" x14ac:dyDescent="0.15">
       <c r="A7" s="8" t="s">
         <v>26</v>
       </c>
@@ -1163,7 +1239,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="132.94999999999999" customHeight="1">
+    <row r="8" spans="1:7" ht="133" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="8"/>
       <c r="B8" s="1" t="s">
         <v>30</v>
@@ -1184,7 +1260,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="198">
+    <row r="9" spans="1:7" ht="152" x14ac:dyDescent="0.15">
       <c r="A9" s="8"/>
       <c r="B9" s="1" t="s">
         <v>33</v>
@@ -1205,7 +1281,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="57" customHeight="1">
+    <row r="10" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="8" t="s">
         <v>36</v>
       </c>
@@ -1228,7 +1304,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="57" customHeight="1">
+    <row r="11" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="8"/>
       <c r="B11" s="1" t="s">
         <v>40</v>
@@ -1249,7 +1325,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="54">
+    <row r="12" spans="1:7" ht="57" x14ac:dyDescent="0.15">
       <c r="A12" s="8"/>
       <c r="B12" s="1" t="s">
         <v>43</v>
@@ -1270,7 +1346,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="72">
+    <row r="13" spans="1:7" ht="57" x14ac:dyDescent="0.15">
       <c r="A13" s="8" t="s">
         <v>46</v>
       </c>
@@ -1293,7 +1369,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="108.95" customHeight="1">
+    <row r="14" spans="1:7" ht="109" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="8"/>
       <c r="B14" s="1" t="s">
         <v>49</v>
@@ -1312,7 +1388,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="72">
+    <row r="15" spans="1:7" ht="76" x14ac:dyDescent="0.15">
       <c r="A15" s="8"/>
       <c r="B15" s="1" t="s">
         <v>52</v>
@@ -1331,7 +1407,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="150.94999999999999" customHeight="1">
+    <row r="16" spans="1:7" ht="151" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="8"/>
       <c r="B16" s="1" t="s">
         <v>55</v>
@@ -1350,7 +1426,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="57" customHeight="1">
+    <row r="17" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="8" t="s">
         <v>58</v>
       </c>
@@ -1373,7 +1449,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="144">
+    <row r="18" spans="1:7" ht="133" x14ac:dyDescent="0.15">
       <c r="A18" s="8"/>
       <c r="B18" s="1" t="s">
         <v>62</v>
@@ -1394,7 +1470,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="75.95" customHeight="1">
+    <row r="19" spans="1:7" ht="76" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="8"/>
       <c r="B19" s="1" t="s">
         <v>66</v>
@@ -1415,7 +1491,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="75.95" customHeight="1">
+    <row r="20" spans="1:7" ht="76" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="8"/>
       <c r="B20" s="1" t="s">
         <v>69</v>
@@ -1436,7 +1512,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="15.75" customHeight="1">
+    <row r="21" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A21" s="1" t="s">
         <v>72</v>
       </c>
@@ -1468,19 +1544,19 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:H21"/>
-  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.5" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="27.85546875" style="2" customWidth="1"/>
-    <col min="2" max="2" width="41.5703125" style="2" customWidth="1"/>
-    <col min="3" max="3" width="20.42578125" style="2" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="27.83203125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="41.5" style="2" customWidth="1"/>
+    <col min="3" max="3" width="20.5" style="2" hidden="1" customWidth="1"/>
     <col min="4" max="5" width="0" style="2" hidden="1" customWidth="1"/>
     <col min="6" max="6" width="59" style="2" customWidth="1"/>
-    <col min="7" max="7" width="102.42578125" style="2" customWidth="1"/>
-    <col min="8" max="8" width="78.28515625" style="2" customWidth="1"/>
-    <col min="9" max="16384" width="12.5703125" style="2"/>
+    <col min="7" max="7" width="102.5" style="2" customWidth="1"/>
+    <col min="8" max="8" width="78.33203125" style="2" customWidth="1"/>
+    <col min="9" max="16384" width="12.5" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="5" customFormat="1" ht="18">
+    <row r="1" spans="1:8" s="5" customFormat="1" ht="38" x14ac:dyDescent="0.15">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1506,7 +1582,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="71.25">
+    <row r="2" spans="1:8" ht="57" x14ac:dyDescent="0.15">
       <c r="A2" s="8" t="s">
         <v>7</v>
       </c>
@@ -1532,7 +1608,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="196.5">
+    <row r="3" spans="1:8" ht="190" x14ac:dyDescent="0.15">
       <c r="A3" s="8"/>
       <c r="B3" s="1" t="s">
         <v>13</v>
@@ -1556,7 +1632,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="143.25">
+    <row r="4" spans="1:8" ht="133" x14ac:dyDescent="0.15">
       <c r="A4" s="8"/>
       <c r="B4" s="1" t="s">
         <v>17</v>
@@ -1571,7 +1647,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="179.1" customHeight="1">
+    <row r="5" spans="1:8" ht="179" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="8"/>
       <c r="B5" s="1" t="s">
         <v>20</v>
@@ -1586,7 +1662,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="108">
+    <row r="6" spans="1:8" ht="95" x14ac:dyDescent="0.15">
       <c r="A6" s="8"/>
       <c r="B6" s="1" t="s">
         <v>23</v>
@@ -1607,7 +1683,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="72">
+    <row r="7" spans="1:8" ht="76" x14ac:dyDescent="0.15">
       <c r="A7" s="8" t="s">
         <v>26</v>
       </c>
@@ -1630,7 +1706,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="132.94999999999999" customHeight="1">
+    <row r="8" spans="1:8" ht="133" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="8"/>
       <c r="B8" s="1" t="s">
         <v>30</v>
@@ -1651,7 +1727,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="198">
+    <row r="9" spans="1:8" ht="152" x14ac:dyDescent="0.15">
       <c r="A9" s="8"/>
       <c r="B9" s="1" t="s">
         <v>33</v>
@@ -1672,7 +1748,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="57" customHeight="1">
+    <row r="10" spans="1:8" ht="57" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="8" t="s">
         <v>36</v>
       </c>
@@ -1695,7 +1771,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="57" customHeight="1">
+    <row r="11" spans="1:8" ht="57" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="8"/>
       <c r="B11" s="1" t="s">
         <v>40</v>
@@ -1716,7 +1792,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="54">
+    <row r="12" spans="1:8" ht="57" x14ac:dyDescent="0.15">
       <c r="A12" s="8"/>
       <c r="B12" s="1" t="s">
         <v>43</v>
@@ -1737,7 +1813,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="72">
+    <row r="13" spans="1:8" ht="57" x14ac:dyDescent="0.15">
       <c r="A13" s="8" t="s">
         <v>46</v>
       </c>
@@ -1760,7 +1836,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="108.95" customHeight="1">
+    <row r="14" spans="1:8" ht="109" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="8"/>
       <c r="B14" s="1" t="s">
         <v>49</v>
@@ -1779,7 +1855,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="72">
+    <row r="15" spans="1:8" ht="76" x14ac:dyDescent="0.15">
       <c r="A15" s="8"/>
       <c r="B15" s="1" t="s">
         <v>52</v>
@@ -1798,7 +1874,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="150.94999999999999" customHeight="1">
+    <row r="16" spans="1:8" ht="151" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="8"/>
       <c r="B16" s="1" t="s">
         <v>55</v>
@@ -1817,7 +1893,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="57" customHeight="1">
+    <row r="17" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="8" t="s">
         <v>58</v>
       </c>
@@ -1840,7 +1916,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="144">
+    <row r="18" spans="1:7" ht="133" x14ac:dyDescent="0.15">
       <c r="A18" s="8"/>
       <c r="B18" s="1" t="s">
         <v>62</v>
@@ -1861,7 +1937,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="75.95" customHeight="1">
+    <row r="19" spans="1:7" ht="76" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="8"/>
       <c r="B19" s="1" t="s">
         <v>66</v>
@@ -1882,7 +1958,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="75.95" customHeight="1">
+    <row r="20" spans="1:7" ht="76" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="8"/>
       <c r="B20" s="1" t="s">
         <v>69</v>
@@ -1903,7 +1979,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="15.75" customHeight="1">
+    <row r="21" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A21" s="1" t="s">
         <v>72</v>
       </c>
@@ -1932,19 +2008,19 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CFDA2219-0132-4978-91E9-4C6E1D53AA06}">
   <dimension ref="A1:H21"/>
-  <sheetFormatPr defaultRowHeight="12.75"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="32.28515625" customWidth="1"/>
-    <col min="2" max="2" width="39.42578125" customWidth="1"/>
-    <col min="3" max="3" width="12.5703125" customWidth="1"/>
-    <col min="4" max="4" width="20.42578125" customWidth="1"/>
-    <col min="5" max="5" width="13.7109375" customWidth="1"/>
-    <col min="6" max="6" width="38.28515625" customWidth="1"/>
-    <col min="7" max="7" width="95.85546875" customWidth="1"/>
-    <col min="8" max="8" width="61.7109375" customWidth="1"/>
+    <col min="1" max="1" width="32.33203125" customWidth="1"/>
+    <col min="2" max="2" width="39.5" customWidth="1"/>
+    <col min="3" max="3" width="12.5" customWidth="1"/>
+    <col min="4" max="4" width="20.5" customWidth="1"/>
+    <col min="5" max="5" width="13.6640625" customWidth="1"/>
+    <col min="6" max="6" width="38.33203125" customWidth="1"/>
+    <col min="7" max="7" width="95.83203125" customWidth="1"/>
+    <col min="8" max="8" width="61.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="36">
+    <row r="1" spans="1:8" ht="19" x14ac:dyDescent="0.15">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1970,7 +2046,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="72">
+    <row r="2" spans="1:8" ht="57" x14ac:dyDescent="0.15">
       <c r="A2" s="8" t="s">
         <v>7</v>
       </c>
@@ -1993,7 +2069,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="252">
+    <row r="3" spans="1:8" ht="228" x14ac:dyDescent="0.15">
       <c r="A3" s="8"/>
       <c r="B3" s="1" t="s">
         <v>13</v>
@@ -2017,7 +2093,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="180">
+    <row r="4" spans="1:8" ht="171" x14ac:dyDescent="0.15">
       <c r="A4" s="8"/>
       <c r="B4" s="1" t="s">
         <v>17</v>
@@ -2035,7 +2111,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="288">
+    <row r="5" spans="1:8" ht="285" x14ac:dyDescent="0.15">
       <c r="A5" s="8"/>
       <c r="B5" s="1" t="s">
         <v>20</v>
@@ -2053,7 +2129,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="108">
+    <row r="6" spans="1:8" ht="95" x14ac:dyDescent="0.15">
       <c r="A6" s="8"/>
       <c r="B6" s="1" t="s">
         <v>23</v>
@@ -2077,7 +2153,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="126">
+    <row r="7" spans="1:8" ht="114" x14ac:dyDescent="0.15">
       <c r="A7" s="8" t="s">
         <v>26</v>
       </c>
@@ -2100,7 +2176,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="144">
+    <row r="8" spans="1:8" ht="133" x14ac:dyDescent="0.15">
       <c r="A8" s="8"/>
       <c r="B8" s="1" t="s">
         <v>30</v>
@@ -2124,7 +2200,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="198">
+    <row r="9" spans="1:8" ht="171" x14ac:dyDescent="0.15">
       <c r="A9" s="8"/>
       <c r="B9" s="1" t="s">
         <v>33</v>
@@ -2148,7 +2224,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="126">
+    <row r="10" spans="1:8" ht="114" x14ac:dyDescent="0.15">
       <c r="A10" s="8" t="s">
         <v>36</v>
       </c>
@@ -2174,7 +2250,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="108">
+    <row r="11" spans="1:8" ht="114" x14ac:dyDescent="0.15">
       <c r="A11" s="8"/>
       <c r="B11" s="1" t="s">
         <v>40</v>
@@ -2195,7 +2271,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="54">
+    <row r="12" spans="1:8" ht="57" x14ac:dyDescent="0.15">
       <c r="A12" s="8"/>
       <c r="B12" s="1" t="s">
         <v>43</v>
@@ -2216,7 +2292,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="72">
+    <row r="13" spans="1:8" ht="76" x14ac:dyDescent="0.15">
       <c r="A13" s="8" t="s">
         <v>46</v>
       </c>
@@ -2242,7 +2318,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="90">
+    <row r="14" spans="1:8" ht="95" x14ac:dyDescent="0.15">
       <c r="A14" s="8"/>
       <c r="B14" s="1" t="s">
         <v>49</v>
@@ -2261,7 +2337,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="72">
+    <row r="15" spans="1:8" ht="76" x14ac:dyDescent="0.15">
       <c r="A15" s="8"/>
       <c r="B15" s="1" t="s">
         <v>52</v>
@@ -2280,7 +2356,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="162">
+    <row r="16" spans="1:8" ht="152" x14ac:dyDescent="0.15">
       <c r="A16" s="8"/>
       <c r="B16" s="1" t="s">
         <v>55</v>
@@ -2299,7 +2375,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="54">
+    <row r="17" spans="1:8" ht="57" x14ac:dyDescent="0.15">
       <c r="A17" s="8" t="s">
         <v>58</v>
       </c>
@@ -2325,7 +2401,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="216">
+    <row r="18" spans="1:8" ht="209" x14ac:dyDescent="0.15">
       <c r="A18" s="8"/>
       <c r="B18" s="1" t="s">
         <v>62</v>
@@ -2349,7 +2425,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="54">
+    <row r="19" spans="1:8" ht="38" x14ac:dyDescent="0.15">
       <c r="A19" s="8"/>
       <c r="B19" s="1" t="s">
         <v>66</v>
@@ -2370,7 +2446,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="20" spans="1:8" ht="126">
+    <row r="20" spans="1:8" ht="114" x14ac:dyDescent="0.15">
       <c r="A20" s="8"/>
       <c r="B20" s="1" t="s">
         <v>69</v>
@@ -2394,7 +2470,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="21" spans="1:8" ht="18">
+    <row r="21" spans="1:8" ht="19" x14ac:dyDescent="0.15">
       <c r="A21" s="1" t="s">
         <v>72</v>
       </c>
@@ -2430,19 +2506,19 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:H21"/>
-  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.5" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="27.85546875" style="2" customWidth="1"/>
-    <col min="2" max="2" width="41.5703125" style="2" customWidth="1"/>
-    <col min="3" max="3" width="20.42578125" style="2" customWidth="1"/>
-    <col min="4" max="5" width="12.5703125" style="2" customWidth="1"/>
+    <col min="1" max="1" width="27.83203125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="41.5" style="2" customWidth="1"/>
+    <col min="3" max="3" width="20.5" style="2" customWidth="1"/>
+    <col min="4" max="5" width="12.5" style="2" customWidth="1"/>
     <col min="6" max="6" width="59" style="2" customWidth="1"/>
-    <col min="7" max="7" width="102.42578125" style="2" customWidth="1"/>
-    <col min="8" max="8" width="62.5703125" style="2" customWidth="1"/>
-    <col min="9" max="16384" width="12.5703125" style="2"/>
+    <col min="7" max="7" width="102.5" style="2" customWidth="1"/>
+    <col min="8" max="8" width="62.5" style="2" customWidth="1"/>
+    <col min="9" max="16384" width="12.5" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="5" customFormat="1" ht="36">
+    <row r="1" spans="1:8" s="5" customFormat="1" ht="38" x14ac:dyDescent="0.15">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -2468,7 +2544,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="72">
+    <row r="2" spans="1:8" ht="57" x14ac:dyDescent="0.15">
       <c r="A2" s="8" t="s">
         <v>7</v>
       </c>
@@ -2491,7 +2567,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="364.5">
+    <row r="3" spans="1:8" ht="190" x14ac:dyDescent="0.15">
       <c r="A3" s="8"/>
       <c r="B3" s="1" t="s">
         <v>13</v>
@@ -2512,7 +2588,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="126">
+    <row r="4" spans="1:8" ht="133" x14ac:dyDescent="0.15">
       <c r="A4" s="8"/>
       <c r="B4" s="1" t="s">
         <v>17</v>
@@ -2530,7 +2606,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="179.1" customHeight="1">
+    <row r="5" spans="1:8" ht="179" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="8"/>
       <c r="B5" s="1" t="s">
         <v>20</v>
@@ -2548,7 +2624,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="108">
+    <row r="6" spans="1:8" ht="95" x14ac:dyDescent="0.15">
       <c r="A6" s="8"/>
       <c r="B6" s="1" t="s">
         <v>23</v>
@@ -2569,7 +2645,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="164.25">
+    <row r="7" spans="1:8" ht="76" x14ac:dyDescent="0.15">
       <c r="A7" s="8" t="s">
         <v>26</v>
       </c>
@@ -2595,7 +2671,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="132.94999999999999" customHeight="1">
+    <row r="8" spans="1:8" ht="133" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="8"/>
       <c r="B8" s="1" t="s">
         <v>30</v>
@@ -2619,7 +2695,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="198">
+    <row r="9" spans="1:8" ht="152" x14ac:dyDescent="0.15">
       <c r="A9" s="8"/>
       <c r="B9" s="1" t="s">
         <v>33</v>
@@ -2640,7 +2716,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="82.5" customHeight="1">
+    <row r="10" spans="1:8" ht="82.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="8" t="s">
         <v>36</v>
       </c>
@@ -2666,7 +2742,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="108">
+    <row r="11" spans="1:8" ht="95" x14ac:dyDescent="0.15">
       <c r="A11" s="8"/>
       <c r="B11" s="1" t="s">
         <v>40</v>
@@ -2687,7 +2763,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="54">
+    <row r="12" spans="1:8" ht="57" x14ac:dyDescent="0.15">
       <c r="A12" s="8"/>
       <c r="B12" s="1" t="s">
         <v>43</v>
@@ -2708,7 +2784,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="72">
+    <row r="13" spans="1:8" ht="57" x14ac:dyDescent="0.15">
       <c r="A13" s="8" t="s">
         <v>46</v>
       </c>
@@ -2734,7 +2810,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="108.95" customHeight="1">
+    <row r="14" spans="1:8" ht="109" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="8"/>
       <c r="B14" s="1" t="s">
         <v>49</v>
@@ -2756,7 +2832,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="72">
+    <row r="15" spans="1:8" ht="76" x14ac:dyDescent="0.15">
       <c r="A15" s="8"/>
       <c r="B15" s="1" t="s">
         <v>52</v>
@@ -2775,7 +2851,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="150.94999999999999" customHeight="1">
+    <row r="16" spans="1:8" ht="151" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="8"/>
       <c r="B16" s="1" t="s">
         <v>55</v>
@@ -2794,7 +2870,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="57" customHeight="1">
+    <row r="17" spans="1:8" ht="57" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="8" t="s">
         <v>58</v>
       </c>
@@ -2820,7 +2896,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="144">
+    <row r="18" spans="1:8" ht="133" x14ac:dyDescent="0.15">
       <c r="A18" s="8"/>
       <c r="B18" s="1" t="s">
         <v>62</v>
@@ -2844,7 +2920,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="75.95" customHeight="1">
+    <row r="19" spans="1:8" ht="76" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="8"/>
       <c r="B19" s="1" t="s">
         <v>66</v>
@@ -2865,7 +2941,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="20" spans="1:8" ht="104.45" customHeight="1">
+    <row r="20" spans="1:8" ht="104.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="8"/>
       <c r="B20" s="1" t="s">
         <v>69</v>
@@ -2889,7 +2965,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="21" spans="1:8" ht="15.75" customHeight="1">
+    <row r="21" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A21" s="1" t="s">
         <v>72</v>
       </c>
@@ -2921,19 +2997,19 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:I21"/>
-  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.5" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="27.85546875" style="2" customWidth="1"/>
-    <col min="2" max="2" width="41.5703125" style="2" customWidth="1"/>
-    <col min="3" max="3" width="20.42578125" style="2" customWidth="1"/>
-    <col min="4" max="5" width="12.5703125" style="2" customWidth="1"/>
+    <col min="1" max="1" width="27.83203125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="41.5" style="2" customWidth="1"/>
+    <col min="3" max="3" width="20.5" style="2" customWidth="1"/>
+    <col min="4" max="5" width="12.5" style="2" customWidth="1"/>
     <col min="6" max="6" width="59" style="2" customWidth="1"/>
-    <col min="7" max="8" width="102.42578125" style="2" customWidth="1"/>
-    <col min="9" max="9" width="62.5703125" style="2" customWidth="1"/>
-    <col min="10" max="16384" width="12.5703125" style="2"/>
+    <col min="7" max="8" width="102.5" style="2" customWidth="1"/>
+    <col min="9" max="9" width="62.5" style="2" customWidth="1"/>
+    <col min="10" max="16384" width="12.5" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="5" customFormat="1" ht="36">
+    <row r="1" spans="1:9" s="5" customFormat="1" ht="38" x14ac:dyDescent="0.15">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -2960,7 +3036,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="71.25">
+    <row r="2" spans="1:9" ht="57" x14ac:dyDescent="0.15">
       <c r="A2" s="8" t="s">
         <v>7</v>
       </c>
@@ -2983,7 +3059,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="196.5">
+    <row r="3" spans="1:9" ht="190" x14ac:dyDescent="0.15">
       <c r="A3" s="8"/>
       <c r="B3" s="1" t="s">
         <v>13</v>
@@ -3004,7 +3080,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="143.25">
+    <row r="4" spans="1:9" ht="133" x14ac:dyDescent="0.15">
       <c r="A4" s="8"/>
       <c r="B4" s="1" t="s">
         <v>17</v>
@@ -3022,7 +3098,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="179.1" customHeight="1">
+    <row r="5" spans="1:9" ht="179" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="8"/>
       <c r="B5" s="1" t="s">
         <v>20</v>
@@ -3040,7 +3116,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="107.25">
+    <row r="6" spans="1:9" ht="95" x14ac:dyDescent="0.15">
       <c r="A6" s="8"/>
       <c r="B6" s="1" t="s">
         <v>23</v>
@@ -3061,7 +3137,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="89.25">
+    <row r="7" spans="1:9" ht="76" x14ac:dyDescent="0.15">
       <c r="A7" s="8" t="s">
         <v>26</v>
       </c>
@@ -3087,7 +3163,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="132.94999999999999" customHeight="1">
+    <row r="8" spans="1:9" ht="133" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="8"/>
       <c r="B8" s="1" t="s">
         <v>30</v>
@@ -3111,7 +3187,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="161.25">
+    <row r="9" spans="1:9" ht="152" x14ac:dyDescent="0.15">
       <c r="A9" s="8"/>
       <c r="B9" s="1" t="s">
         <v>33</v>
@@ -3132,7 +3208,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="82.5" customHeight="1">
+    <row r="10" spans="1:9" ht="82.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="8" t="s">
         <v>36</v>
       </c>
@@ -3158,7 +3234,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="125.25">
+    <row r="11" spans="1:9" ht="95" x14ac:dyDescent="0.15">
       <c r="A11" s="8"/>
       <c r="B11" s="1" t="s">
         <v>40</v>
@@ -3179,7 +3255,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="54">
+    <row r="12" spans="1:9" ht="57" x14ac:dyDescent="0.15">
       <c r="A12" s="8"/>
       <c r="B12" s="1" t="s">
         <v>43</v>
@@ -3201,7 +3277,7 @@
       </c>
       <c r="H12" s="1"/>
     </row>
-    <row r="13" spans="1:9" ht="71.25">
+    <row r="13" spans="1:9" ht="57" x14ac:dyDescent="0.15">
       <c r="A13" s="8" t="s">
         <v>46</v>
       </c>
@@ -3227,7 +3303,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="108.95" customHeight="1">
+    <row r="14" spans="1:9" ht="109" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="8"/>
       <c r="B14" s="1" t="s">
         <v>49</v>
@@ -3249,7 +3325,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="71.25">
+    <row r="15" spans="1:9" ht="76" x14ac:dyDescent="0.15">
       <c r="A15" s="8"/>
       <c r="B15" s="1" t="s">
         <v>52</v>
@@ -3268,7 +3344,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="150.94999999999999" customHeight="1">
+    <row r="16" spans="1:9" ht="151" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="8"/>
       <c r="B16" s="1" t="s">
         <v>55</v>
@@ -3287,7 +3363,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="17" spans="1:9" ht="57" customHeight="1">
+    <row r="17" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="8" t="s">
         <v>58</v>
       </c>
@@ -3313,7 +3389,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="18" spans="1:9" ht="178.5">
+    <row r="18" spans="1:9" ht="133" x14ac:dyDescent="0.15">
       <c r="A18" s="8"/>
       <c r="B18" s="1" t="s">
         <v>62</v>
@@ -3337,7 +3413,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="19" spans="1:9" ht="75.95" customHeight="1">
+    <row r="19" spans="1:9" ht="76" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="8"/>
       <c r="B19" s="1" t="s">
         <v>66</v>
@@ -3358,7 +3434,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="20" spans="1:9" ht="104.45" customHeight="1">
+    <row r="20" spans="1:9" ht="104.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="8"/>
       <c r="B20" s="1" t="s">
         <v>69</v>
@@ -3382,7 +3458,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="21" spans="1:9" ht="15.75" customHeight="1">
+    <row r="21" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A21" s="1" t="s">
         <v>72</v>
       </c>
@@ -3414,20 +3490,20 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:H21"/>
-  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.5" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="15.28515625" style="2" customWidth="1"/>
-    <col min="2" max="2" width="35" style="2" customWidth="1"/>
-    <col min="3" max="3" width="5.5703125" style="2" customWidth="1"/>
-    <col min="4" max="4" width="12.5703125" style="2" customWidth="1"/>
-    <col min="5" max="5" width="6.7109375" style="2" customWidth="1"/>
-    <col min="6" max="6" width="59" style="2" customWidth="1"/>
-    <col min="7" max="7" width="102.42578125" style="2" customWidth="1"/>
-    <col min="8" max="8" width="62.5703125" style="2" customWidth="1"/>
-    <col min="9" max="16384" width="12.5703125" style="2"/>
+    <col min="1" max="1" width="29.1640625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="51.5" style="2" customWidth="1"/>
+    <col min="3" max="3" width="11.1640625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="12.5" style="2" customWidth="1"/>
+    <col min="5" max="5" width="6.6640625" style="2" customWidth="1"/>
+    <col min="6" max="6" width="64.83203125" style="2" customWidth="1"/>
+    <col min="7" max="7" width="102.5" style="2" customWidth="1"/>
+    <col min="8" max="8" width="62.5" style="2" customWidth="1"/>
+    <col min="9" max="16384" width="12.5" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="5" customFormat="1" ht="36">
+    <row r="1" spans="1:8" s="5" customFormat="1" ht="38" x14ac:dyDescent="0.15">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -3450,10 +3526,10 @@
         <v>86</v>
       </c>
       <c r="H1" s="7" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" ht="72">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="114" x14ac:dyDescent="0.15">
       <c r="A2" s="8" t="s">
         <v>7</v>
       </c>
@@ -3475,8 +3551,11 @@
       <c r="G2" s="2" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" ht="364.5">
+      <c r="H2" s="2" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="190" x14ac:dyDescent="0.15">
       <c r="A3" s="8"/>
       <c r="B3" s="1" t="s">
         <v>13</v>
@@ -3496,8 +3575,11 @@
       <c r="G3" s="2" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" ht="126">
+      <c r="H3" s="2" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="133" x14ac:dyDescent="0.15">
       <c r="A4" s="8"/>
       <c r="B4" s="1" t="s">
         <v>17</v>
@@ -3512,10 +3594,10 @@
         <v>91</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="179.1" customHeight="1">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="179" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="8"/>
       <c r="B5" s="1" t="s">
         <v>20</v>
@@ -3530,10 +3612,10 @@
         <v>94</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="108">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="95" x14ac:dyDescent="0.15">
       <c r="A6" s="8"/>
       <c r="B6" s="1" t="s">
         <v>23</v>
@@ -3553,8 +3635,11 @@
       <c r="G6" s="2" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="7" spans="1:8" ht="164.25">
+      <c r="H6" s="2" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="114" x14ac:dyDescent="0.15">
       <c r="A7" s="8" t="s">
         <v>26</v>
       </c>
@@ -3577,10 +3662,10 @@
         <v>99</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" ht="132.94999999999999" customHeight="1">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="133" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="8"/>
       <c r="B8" s="1" t="s">
         <v>30</v>
@@ -3601,10 +3686,10 @@
         <v>102</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" ht="198">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="133" x14ac:dyDescent="0.15">
       <c r="A9" s="8"/>
       <c r="B9" s="1" t="s">
         <v>33</v>
@@ -3624,8 +3709,11 @@
       <c r="G9" s="2" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="10" spans="1:8" ht="82.5" customHeight="1">
+      <c r="H9" s="2" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="82.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="8" t="s">
         <v>36</v>
       </c>
@@ -3648,10 +3736,10 @@
         <v>107</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" ht="108">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="95" x14ac:dyDescent="0.15">
       <c r="A11" s="8"/>
       <c r="B11" s="1" t="s">
         <v>40</v>
@@ -3671,8 +3759,11 @@
       <c r="G11" s="2" t="s">
         <v>110</v>
       </c>
-    </row>
-    <row r="12" spans="1:8" ht="54">
+      <c r="H11" s="2" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="95" x14ac:dyDescent="0.15">
       <c r="A12" s="8"/>
       <c r="B12" s="1" t="s">
         <v>43</v>
@@ -3692,8 +3783,11 @@
       <c r="G12" s="1" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="13" spans="1:8" ht="72">
+      <c r="H12" s="2" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="95" x14ac:dyDescent="0.15">
       <c r="A13" s="8" t="s">
         <v>46</v>
       </c>
@@ -3716,10 +3810,10 @@
         <v>48</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" ht="108.95" customHeight="1">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="109" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="8"/>
       <c r="B14" s="1" t="s">
         <v>49</v>
@@ -3738,10 +3832,10 @@
         <v>114</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" ht="72">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="114" x14ac:dyDescent="0.15">
       <c r="A15" s="8"/>
       <c r="B15" s="1" t="s">
         <v>52</v>
@@ -3759,8 +3853,11 @@
       <c r="G15" s="2" t="s">
         <v>116</v>
       </c>
-    </row>
-    <row r="16" spans="1:8" ht="150.94999999999999" customHeight="1">
+      <c r="H15" s="2" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="151" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="8"/>
       <c r="B16" s="1" t="s">
         <v>55</v>
@@ -3778,8 +3875,11 @@
       <c r="G16" s="2" t="s">
         <v>118</v>
       </c>
-    </row>
-    <row r="17" spans="1:8" ht="57" customHeight="1">
+      <c r="H16" s="2" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="100" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="8" t="s">
         <v>58</v>
       </c>
@@ -3802,10 +3902,10 @@
         <v>120</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" ht="144">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="133" x14ac:dyDescent="0.15">
       <c r="A18" s="8"/>
       <c r="B18" s="1" t="s">
         <v>62</v>
@@ -3826,10 +3926,10 @@
         <v>122</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" ht="75.95" customHeight="1">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" ht="76" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="8"/>
       <c r="B19" s="1" t="s">
         <v>66</v>
@@ -3850,7 +3950,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="20" spans="1:8" ht="104.45" customHeight="1">
+    <row r="20" spans="1:8" ht="104.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="8"/>
       <c r="B20" s="1" t="s">
         <v>69</v>
@@ -3871,10 +3971,10 @@
         <v>126</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" ht="15.75" customHeight="1">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A21" s="1" t="s">
         <v>72</v>
       </c>
@@ -3901,6 +4001,27 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_Flow_SignoffStatus xmlns="f7054c2e-66b3-498e-9cd3-8fc0b7b9ae61" xsi:nil="true"/>
+    <TaxCatchAll xmlns="31dbb24d-15c9-472f-8e66-282623661095" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f7054c2e-66b3-498e-9cd3-8fc0b7b9ae61">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101001A785ADC7107744187DF4CC27E0E488D" ma:contentTypeVersion="17" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="172d67baf4fc410fcd4be9ea8666f4da">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f7054c2e-66b3-498e-9cd3-8fc0b7b9ae61" xmlns:ns3="31dbb24d-15c9-472f-8e66-282623661095" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="b05c6aec39b3eb6a6226c7cac4e33a6b" ns2:_="" ns3:_="">
     <xsd:import namespace="f7054c2e-66b3-498e-9cd3-8fc0b7b9ae61"/>
@@ -4147,37 +4268,42 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_Flow_SignoffStatus xmlns="f7054c2e-66b3-498e-9cd3-8fc0b7b9ae61" xsi:nil="true"/>
-    <TaxCatchAll xmlns="31dbb24d-15c9-472f-8e66-282623661095" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f7054c2e-66b3-498e-9cd3-8fc0b7b9ae61">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{53CCF363-15AC-4070-AB91-F616E73C882F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A7F38187-1F1A-447E-A511-B8451543E6CB}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{01F0BBE8-220F-4EB0-ADC6-A2436B653351}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{01F0BBE8-220F-4EB0-ADC6-A2436B653351}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="f7054c2e-66b3-498e-9cd3-8fc0b7b9ae61"/>
+    <ds:schemaRef ds:uri="31dbb24d-15c9-472f-8e66-282623661095"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A7F38187-1F1A-447E-A511-B8451543E6CB}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{53CCF363-15AC-4070-AB91-F616E73C882F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="f7054c2e-66b3-498e-9cd3-8fc0b7b9ae61"/>
+    <ds:schemaRef ds:uri="31dbb24d-15c9-472f-8e66-282623661095"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
